--- a/results/auto_Cape_Town_Environmental.xlsx
+++ b/results/auto_Cape_Town_Environmental.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -37,28 +37,10 @@
     <t>Sent</t>
   </si>
   <si>
-    <t>SANCCOB</t>
-  </si>
-  <si>
-    <t>Greenpop</t>
-  </si>
-  <si>
-    <t>Cape Leopard Trust</t>
-  </si>
-  <si>
-    <t>WESSA Western Cape</t>
-  </si>
-  <si>
-    <t>Friends of Table Mountain</t>
-  </si>
-  <si>
-    <t>Cape Town Environmental Education Trust (CTEET)</t>
-  </si>
-  <si>
-    <t>Kirstenbosch Volunteers</t>
-  </si>
-  <si>
-    <t>Sustainable Seas Trust</t>
+    <t>Abalimi Bezekhaya</t>
+  </si>
+  <si>
+    <t>Communitree</t>
   </si>
   <si>
     <t>Environmental</t>
@@ -67,28 +49,16 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>info@sanccob.co.za</t>
-  </si>
-  <si>
-    <t>info@greenpop.org</t>
-  </si>
-  <si>
-    <t>clt@capeleopard.org.za</t>
-  </si>
-  <si>
-    <t>wc@wessa.co.za</t>
-  </si>
-  <si>
-    <t>info@fotm.org.za</t>
-  </si>
-  <si>
-    <t>info@cteet.co.za</t>
-  </si>
-  <si>
-    <t>volunteers@sanbi.org.za</t>
-  </si>
-  <si>
-    <t>info@sst.org.za</t>
+    <t>info@abalimi.org.za</t>
+  </si>
+  <si>
+    <t>info@communitree.org</t>
+  </si>
+  <si>
+    <t>021 371 1653</t>
+  </si>
+  <si>
+    <t>www.abalimi.org.za</t>
   </si>
   <si>
     <t>Yes</t>
@@ -423,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -454,16 +424,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
         <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -471,118 +447,16 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
